--- a/docs/test-case/unit-test-case.xlsx
+++ b/docs/test-case/unit-test-case.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3d375f96120bad62/Desktop/課題対応/家計簿Webアプリ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="312" documentId="8_{DDF862CF-F143-4CC9-A6CA-14BC15AC551D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47C7FB6B-F4A4-4018-8AAC-B8B1B97D71B8}"/>
+  <xr:revisionPtr revIDLastSave="422" documentId="8_{DDF862CF-F143-4CC9-A6CA-14BC15AC551D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8888CB4C-054F-41A7-9354-FCF60B99B57D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A3991131-F50F-48C8-A668-424B1E8F7C7F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{A3991131-F50F-48C8-A668-424B1E8F7C7F}"/>
   </bookViews>
   <sheets>
-    <sheet name="テストケース_トップページ" sheetId="6" r:id="rId1"/>
-    <sheet name="テストケース_予算設定" sheetId="3" r:id="rId2"/>
-    <sheet name="テストケース_支出一覧" sheetId="4" r:id="rId3"/>
+    <sheet name="不具合一覧表" sheetId="7" r:id="rId1"/>
+    <sheet name="テストケース_TopPageService" sheetId="6" r:id="rId2"/>
+    <sheet name="テストケース_BudgetService" sheetId="3" r:id="rId3"/>
+    <sheet name="テストケース_ExpenseService" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">テストケース_予算設定!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">テストケース_BudgetService!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">テストケース_ExpenseService!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">テストケース_TopPageService!$A$1:$G$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="257">
   <si>
     <t>ID</t>
   </si>
@@ -68,9 +71,6 @@
   </si>
   <si>
     <t>1日</t>
-  </si>
-  <si>
-    <t>食費の残金は20,000円</t>
   </si>
   <si>
     <t>TOP-001</t>
@@ -109,10 +109,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>食費の予算40,000円、支出12,000円と8,000円</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>食費の支出なし</t>
     <rPh sb="0" eb="2">
       <t>ショクヒ</t>
@@ -149,16 +145,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カテゴリ別残金</t>
-    <rPh sb="4" eb="5">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ザンキン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -316,9 +302,6 @@
     <t>合計20,000円</t>
   </si>
   <si>
-    <t>EXP-013</t>
-  </si>
-  <si>
     <t>支出が1件、金額5,000円</t>
   </si>
   <si>
@@ -838,9 +821,6 @@
     <t>カテゴリ：食費（ID 1）。支出：10/05, ID 1, 12,000円、10/06, ID 1, 8,000円</t>
   </si>
   <si>
-    <t>カテゴリ：食費（ID 1）。確定予算：40,000円。支出Map：{1: 20,000円}</t>
-  </si>
-  <si>
     <t>支出：10/05, 12,000円、10/06, 8,000円</t>
   </si>
   <si>
@@ -1425,6 +1405,114 @@
   </si>
   <si>
     <t>10/05, 食費, 1,000円, 満足度3、 11/01, 食費, 2,000円, 満足度5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合格</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウカク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストデータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原因</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事象</t>
+    <rPh sb="0" eb="2">
+      <t>ジショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前リストに満足度 3の名前が返却される</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>マンゾクド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヘンキャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最低値の初期値を60%にしているため、最初のカテゴリの満足度が60%の場合、percent == lowestPercent が成立する。その結果、60%未満だけを対象にする仕様にもかかわらず、else if でカテゴリ名が追加されていた。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対応方法</t>
+    <rPh sb="0" eb="4">
+      <t>タイオウホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>else if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> の条件に </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>percent &lt; 60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を追加する。これにより、満足度が60%のカテゴリは名前リストに追加せず、60%未満のカテゴリだけを対象にできる。</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再テスト</t>
+    <rPh sb="0" eb="1">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不合格
+↓
+合格</t>
+    <rPh sb="0" eb="3">
+      <t>フゴウカク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゴウカク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1468,13 +1556,11 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Arial Unicode MS"/>
       <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
@@ -1517,7 +1603,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1548,23 +1634,41 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1903,6 +2007,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E38747F-5198-4155-802E-8F8FD9BBBEF0}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="36.625" customWidth="1"/>
+    <col min="7" max="7" width="50.75" customWidth="1"/>
+    <col min="8" max="8" width="44.625" customWidth="1"/>
+    <col min="9" max="9" width="9" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="75">
+      <c r="A2" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8E3A01-6074-4C2F-9E8B-C4E9F8865548}">
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -1912,7 +2092,8 @@
     <col min="3" max="3" width="27.625" style="5" customWidth="1"/>
     <col min="4" max="4" width="32.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="33.75" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="5"/>
+    <col min="6" max="6" width="9" style="15"/>
+    <col min="7" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1920,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1929,40 +2110,42 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C2" s="6">
         <v>46296</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2" s="7"/>
+        <v>224</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C3" s="6">
         <v>46310</v>
@@ -1971,17 +2154,19 @@
         <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="F3" s="7"/>
+        <v>225</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C4" s="6">
         <v>46326</v>
@@ -1990,966 +2175,474 @@
         <v>7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="7"/>
+        <v>173</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F5" s="7"/>
+        <v>226</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F6" s="7"/>
+        <v>227</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F7" s="7"/>
+        <v>224</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F8" s="7"/>
+        <v>228</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F9" s="7"/>
+        <v>229</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F10" s="7"/>
+        <v>230</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F11" s="7"/>
+        <v>231</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="37.5">
       <c r="A12" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F12" s="7"/>
+        <v>232</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="37.5">
       <c r="A13" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F13" s="7"/>
+        <v>233</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="37.5">
       <c r="A14" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F14" s="7"/>
+        <v>234</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="37.5">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F15" s="7"/>
+        <v>235</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="37.5">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F16" s="7"/>
+        <v>236</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F17" s="7"/>
+        <v>171</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D18" s="8">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F18" s="7"/>
+        <v>237</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D19" s="8">
         <v>0.2</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F19" s="7"/>
+        <v>238</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D20" s="8">
         <v>0.75</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F20" s="7"/>
+        <v>239</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F21" s="7"/>
+        <v>240</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" ht="37.5">
       <c r="A22" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F22" s="7"/>
+        <v>241</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" ht="37.5">
       <c r="A23" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="F23" s="7"/>
+        <v>242</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" ht="37.5">
+    <row r="24" spans="1:7" ht="56.25">
       <c r="A24" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F24" s="7"/>
+        <v>244</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" ht="37.5">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F25" s="7"/>
+        <v>245</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" ht="37.5">
       <c r="A26" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F26" s="7"/>
+        <v>172</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G26" s="7"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAEA1CD-1929-4D2B-8EDC-FC8BB6D380D8}">
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
-  <cols>
-    <col min="1" max="1" width="9" style="10"/>
-    <col min="2" max="2" width="22.25" style="10" customWidth="1"/>
-    <col min="3" max="3" width="32.25" style="10" customWidth="1"/>
-    <col min="4" max="4" width="34.25" style="10" customWidth="1"/>
-    <col min="5" max="5" width="31.625" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9" style="10"/>
-    <col min="7" max="7" width="11.125" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="37.5">
-      <c r="A2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:7" ht="37.5">
-      <c r="A3" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-    </row>
-    <row r="5" spans="1:7" ht="57.75" customHeight="1">
-      <c r="A5" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-    </row>
-    <row r="6" spans="1:7" ht="37.5">
-      <c r="A6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8" spans="1:7" ht="37.5">
-      <c r="A8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-    </row>
-    <row r="9" spans="1:7" ht="37.5">
-      <c r="A9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:7" ht="37.5">
-      <c r="A10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-    </row>
-    <row r="12" spans="1:7" ht="37.5">
-      <c r="A12" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-    </row>
-    <row r="14" spans="1:7" ht="37.5">
-      <c r="A14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-    </row>
-    <row r="16" spans="1:7" ht="37.5">
-      <c r="A16" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="1:7" ht="37.5">
-      <c r="A18" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="1:7" ht="37.5">
-      <c r="A19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:7" ht="37.5">
-      <c r="A20" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:7" ht="56.25">
-      <c r="A21" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="1:7" ht="56.25">
-      <c r="A22" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="1:7" ht="56.25">
-      <c r="A23" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="1:7" ht="56.25">
-      <c r="A24" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:7" ht="33">
-      <c r="A26" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2958,20 +2651,609 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCAEA1CD-1929-4D2B-8EDC-FC8BB6D380D8}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="22.25" customWidth="1"/>
+    <col min="3" max="3" width="32.25" customWidth="1"/>
+    <col min="4" max="4" width="34.25" customWidth="1"/>
+    <col min="5" max="5" width="31.625" customWidth="1"/>
+    <col min="6" max="6" width="9" style="16"/>
+    <col min="7" max="7" width="11.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="37.5">
+      <c r="A2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" ht="37.5">
+      <c r="A3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G3" s="11"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" ht="57.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G5" s="11"/>
+    </row>
+    <row r="6" spans="1:7" ht="37.5">
+      <c r="A6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="1:7" ht="37.5">
+      <c r="A8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="1:7" ht="37.5">
+      <c r="A9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" ht="37.5">
+      <c r="A10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" ht="37.5">
+      <c r="A12" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:7" ht="37.5">
+      <c r="A14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:7" ht="37.5">
+      <c r="A16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G16" s="11"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" spans="1:7" ht="37.5">
+      <c r="A18" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" spans="1:7" ht="37.5">
+      <c r="A19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" spans="1:7" ht="37.5">
+      <c r="A20" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" spans="1:7" ht="56.25">
+      <c r="A21" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G21" s="11"/>
+    </row>
+    <row r="22" spans="1:7" ht="56.25">
+      <c r="A22" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" ht="56.25">
+      <c r="A23" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="1:7" ht="56.25">
+      <c r="A24" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="1:7" ht="33">
+      <c r="A26" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D757E82-6123-421C-8B05-1E27C068BAC2}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
     <col min="2" max="2" width="24.25" style="5" customWidth="1"/>
     <col min="3" max="4" width="38.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="31.625" style="5" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="5"/>
+    <col min="6" max="6" width="9" style="15"/>
+    <col min="7" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2983,261 +3265,269 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="37.5">
       <c r="A2" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" ht="56.25">
       <c r="A3" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>197</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" ht="75">
       <c r="A4" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>198</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7" ht="37.5">
       <c r="A5" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7" ht="37.5">
       <c r="A6" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>199</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7" ht="37.5">
       <c r="A7" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>171</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7" ht="37.5">
       <c r="A8" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>246</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7" ht="37.5">
       <c r="A9" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F9" s="7"/>
+        <v>200</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="56.25">
       <c r="A10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="37.5">
+      <c r="A11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:7" ht="56.25">
-      <c r="A11" s="7" t="s">
+      <c r="B11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" ht="37.5">
-      <c r="A12" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="B12" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F12" s="7"/>
+        <v>203</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F13" s="7"/>
+        <v>171</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>247</v>
+      </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:7">
       <c r="E15" s="9"/>
@@ -3274,9 +3564,6 @@
     </row>
     <row r="26" spans="5:5">
       <c r="E26" s="9"/>
-    </row>
-    <row r="27" spans="5:5">
-      <c r="E27" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
